--- a/templates/4_KiemKe.xlsx
+++ b/templates/4_KiemKe.xlsx
@@ -149,19 +149,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_KiemKe" displayName="tbl_KiemKe" ref="A1:J2" headerRowCount="1">
-  <autoFilter ref="A1:J2"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Mã chi tiết"/>
-    <tableColumn id="2" name="Tên thiết bị"/>
-    <tableColumn id="3" name="Phòng"/>
-    <tableColumn id="4" name="Đợt kiểm kê"/>
-    <tableColumn id="5" name="SL sổ sách"/>
-    <tableColumn id="6" name="SL thực tế"/>
-    <tableColumn id="7" name="Tình trạng"/>
-    <tableColumn id="8" name="Người kiểm kê"/>
-    <tableColumn id="9" name="Ngày kiểm kê"/>
-    <tableColumn id="10" name="Ghi chú"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_KiemKe" displayName="tbl_KiemKe" ref="A1:S2" headerRowCount="1">
+  <autoFilter ref="A1:S2"/>
+  <tableColumns count="19">
+    <tableColumn id="1" name="Mã số tài sản"/>
+    <tableColumn id="2" name="STT"/>
+    <tableColumn id="3" name="Tên tài sản"/>
+    <tableColumn id="4" name="Đặc điểm"/>
+    <tableColumn id="5" name="ĐVT"/>
+    <tableColumn id="6" name="Số lượng"/>
+    <tableColumn id="7" name="Số lượng kiểm kê"/>
+    <tableColumn id="8" name="Ghi chú"/>
+    <tableColumn id="9" name="Quản lý thiết bị"/>
+    <tableColumn id="10" name="Nơi sử dụng"/>
+    <tableColumn id="11" name="Quản lý phòng"/>
+    <tableColumn id="12" name="Trạng thái"/>
+    <tableColumn id="13" name="Ngày kiểm kê"/>
+    <tableColumn id="14" name="Trạng thái kiểm kê"/>
+    <tableColumn id="15" name="Ngày xác nhận"/>
+    <tableColumn id="16" name="Trạng thái xác nhận"/>
+    <tableColumn id="17" name="Đợt kiểm kê"/>
+    <tableColumn id="18" name="Người kiểm kê"/>
+    <tableColumn id="19" name="Người xác nhận"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -456,114 +465,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mã chi tiết</t>
+          <t>Mã số tài sản</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tên thiết bị</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Phòng</t>
+          <t>Tên tài sản</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Đặc điểm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ĐVT</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Số lượng</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Số lượng kiểm kê</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Quản lý thiết bị</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Nơi sử dụng</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Quản lý phòng</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Ngày kiểm kê</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Trạng thái kiểm kê</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Ngày xác nhận</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Trạng thái xác nhận</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Đợt kiểm kê</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>SL sổ sách</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SL thực tế</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Tình trạng</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Người kiểm kê</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Ngày kiểm kê</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Người xác nhận</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>111028-00001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Máy chiếu</t>
-        </is>
+          <t>111042</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trệt_PH001</t>
+          <t>Tivi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Năm học 2026-2027</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
+          <t>Sharp, 58 inch, UE630X</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Lê Thiên An</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bảo vệ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Nguyễn Trọng Hòa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Đã kiểm kê</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Đợt 2 năm 2024 - 2025</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>kiemke@truong.edu.vn</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -579,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -590,7 +684,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>List SharePoint: KiemKe</t>
+          <t>List SharePoint: Data_Thietbi</t>
         </is>
       </c>
     </row>
@@ -628,7 +722,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mã chi tiết</t>
+          <t>Mã số tài sản</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -641,12 +735,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tên thiết bị</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Một dòng văn bản (Single line of text)</t>
+          <t>Số (Number)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -654,7 +748,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Phòng</t>
+          <t>Tên tài sản</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -667,12 +761,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Đợt kiểm kê</t>
+          <t>Đặc điểm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Một dòng văn bản (Single line of text)</t>
+          <t>Nhiều dòng văn bản (Multiple lines of text)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -680,12 +774,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SL sổ sách</t>
+          <t>ĐVT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Số (Number)</t>
+          <t>Một dòng văn bản (Single line of text)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -693,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SL thực tế</t>
+          <t>Số lượng</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -703,36 +797,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1 = có mặt, 0 = không tìm thấy</t>
+          <t>Số lượng sổ sách = tổng thiết bị cùng Mã tài sản + Đặc điểm + Nơi sử dụng</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tình trạng</t>
+          <t>Số lượng kiểm kê</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Một dòng văn bản (Single line of text)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Gợi ý: Mới, Bình thường, Cần kiểm tra, Cần sửa chữa, Cần thanh lý, Đã thanh lý, Mất</t>
-        </is>
-      </c>
+          <t>Số (Number)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Người kiểm kê</t>
+          <t>Ghi chú</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Một dòng văn bản (Single line of text)</t>
+          <t>Nhiều dòng văn bản (Multiple lines of text)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -740,12 +830,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ngày kiểm kê</t>
+          <t>Quản lý thiết bị</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ngày (Date and time – chỉ ngày)</t>
+          <t>Một dòng văn bản (Single line of text)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -753,15 +843,156 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Nơi sử dụng</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nhiều dòng văn bản (Multiple lines of text)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mã phòng (trùng cột Mã phòng của list Phong); 'Thanh lý' = đã đưa đi thanh lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quản lý phòng</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Email người quản lý phòng – người này thấy phòng ở mục Người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ngày kiểm kê</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ngày (Date and time – chỉ ngày)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Trạng thái kiểm kê</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Đang kiểm kê / Đã kiểm kê (app ghi khi bấm Xác nhận kiểm kê)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ngày xác nhận</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ngày (Date and time – chỉ ngày)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Trạng thái xác nhận</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Đã xác nhận / Không đồng ý (quản lý phòng xác nhận)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Đợt kiểm kê</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Người kiểm kê</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Không bắt buộc – có cột thì app ghi email người kiểm kê</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Người xác nhận</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Một dòng văn bản (Single line of text)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Không bắt buộc – có cột thì app ghi email người xác nhận</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/4_KiemKe.xlsx
+++ b/templates/4_KiemKe.xlsx
@@ -616,7 +616,6 @@
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Lê Thiên An</t>
@@ -646,7 +645,6 @@
         </is>
       </c>
       <c r="O2" s="2" t="n"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>Đợt 2 năm 2024 - 2025</t>
@@ -657,7 +655,6 @@
           <t>kiemke@truong.edu.vn</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
